--- a/Result/profitability/1460.xlsx
+++ b/Result/profitability/1460.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06000000000000001</v>
+        <v>-0.04750000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>14.20875</v>
+        <v>14.69875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05000000000000002</v>
+        <v>-0.06500000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>14.19125</v>
+        <v>14.28</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08625000000000002</v>
+        <v>-0.10875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.57</v>
+        <v>12.27</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.18</v>
+        <v>-0.16875</v>
       </c>
       <c r="N5" t="n">
-        <v>9.52875</v>
+        <v>9.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.14125</v>
+        <v>-0.145</v>
       </c>
       <c r="N6" t="n">
-        <v>9.96875</v>
+        <v>10.1025</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1225</v>
+        <v>-0.14</v>
       </c>
       <c r="N7" t="n">
-        <v>10.55125</v>
+        <v>10.2525</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,13 +1395,13 @@
         <v>-0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14</v>
+        <v>-0.15875</v>
       </c>
       <c r="N8" t="n">
-        <v>10.10125</v>
+        <v>9.654999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1334</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1146</v>
+      </c>
+      <c r="E75" t="n">
+        <v>188</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-87</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-95</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-90</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07625000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.30125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.201923076923077</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4090909090909091</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.129999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08705701078582417</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
